--- a/artfynd/S 1703-2024 artfynd.xlsx
+++ b/artfynd/S 1703-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -811,6 +816,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -950,6 +960,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254190</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1089,6 +1104,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254191</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1228,6 +1248,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254263</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1367,6 +1392,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254792</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1506,6 +1536,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254917</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1645,6 +1680,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254918</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1784,6 +1824,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254535</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1923,6 +1968,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2032,6 +2082,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112301033</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2172,6 +2227,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571419</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2307,6 +2367,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096377</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2447,6 +2512,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571481</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2582,6 +2652,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096456</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2717,6 +2792,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096442</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2847,6 +2927,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571432</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2977,6 +3062,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096395</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3107,6 +3197,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571460</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3237,6 +3332,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096427</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3367,6 +3467,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571478</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3497,6 +3602,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096450</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3632,6 +3742,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096417</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3762,6 +3877,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571450</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3892,6 +4012,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096414</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4022,6 +4147,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571440</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4152,6 +4282,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096402</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4292,6 +4427,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571424</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4427,6 +4567,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096384</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4557,6 +4702,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98571414</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4687,6 +4837,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107096385</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4801,6 +4956,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112300266</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4915,6 +5075,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112300991</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5029,6 +5194,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112301041</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5153,6 +5323,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69538213</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5274,6 +5449,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69532514</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5404,6 +5584,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114307080</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5543,6 +5728,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254265</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5682,6 +5872,11 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122254266</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5812,8 +6007,54 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114307253</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>